--- a/data/trans_dic/P39A2_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P39A2_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que sentirse débil mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que sentirse débil mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 90,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>64,37; 76,82</t>
+          <t>65,13; 77,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>64,3; 73,04</t>
+          <t>64,44; 72,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66,4; 73,86</t>
+          <t>66,24; 73,64</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>66,89; 76,85</t>
+          <t>66,2; 76,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62,0; 69,78</t>
+          <t>61,64; 69,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65,43; 71,63</t>
+          <t>65,52; 72,23</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54,66; 65,87</t>
+          <t>55,12; 66,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45,88; 56,21</t>
+          <t>45,18; 55,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51,72; 59,39</t>
+          <t>51,75; 59,27</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,83; 97,03</t>
+          <t>91,46; 96,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,0; 93,11</t>
+          <t>41,36; 93,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51,73; 93,94</t>
+          <t>56,58; 94,15</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,7; 36,73</t>
+          <t>24,01; 36,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,41; 24,34</t>
+          <t>16,8; 24,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21,54; 28,6</t>
+          <t>21,28; 28,24</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>77,92; 87,03</t>
+          <t>77,48; 87,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>82,48; 89,52</t>
+          <t>82,03; 89,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81,76; 87,37</t>
+          <t>81,16; 87,25</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>43,55; 53,98</t>
+          <t>43,58; 54,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>41,71; 81,1</t>
+          <t>42,14; 81,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45,03; 70,94</t>
+          <t>45,1; 71,89</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>93,25; 98,2</t>
+          <t>93,25; 98,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>92,5; 95,81</t>
+          <t>92,63; 95,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>93,63; 97,39</t>
+          <t>93,44; 97,44</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>70,52; 80,25</t>
+          <t>70,48; 79,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>64,1; 74,0</t>
+          <t>63,93; 74,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>68,3; 75,17</t>
+          <t>68,02; 75,06</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que sentirse débil mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que sentirse débil mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 90,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>200011; 238679</t>
+          <t>202372; 239721</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>182408; 207212</t>
+          <t>182821; 207035</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>394704; 439054</t>
+          <t>393743; 437703</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>339333; 389849</t>
+          <t>335801; 389833</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>298454; 335882</t>
+          <t>296720; 334382</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>646867; 708200</t>
+          <t>647780; 714101</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>152427; 183679</t>
+          <t>153706; 185236</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>133023; 162986</t>
+          <t>130989; 161939</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>294145; 337800</t>
+          <t>294354; 337126</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>221279; 236386</t>
+          <t>222813; 236165</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>153246; 339753</t>
+          <t>150924; 340742</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>314816; 571658</t>
+          <t>344326; 572928</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>43166; 64177</t>
+          <t>41952; 64239</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>33878; 50264</t>
+          <t>34684; 50856</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>82135; 109029</t>
+          <t>81119; 107670</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>190571; 212832</t>
+          <t>189489; 212954</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>185084; 200879</t>
+          <t>184077; 201124</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>383443; 409718</t>
+          <t>380607; 409148</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>247947; 307322</t>
+          <t>248116; 309978</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>324885; 631720</t>
+          <t>328228; 634870</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>607188; 956422</t>
+          <t>608132; 969253</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>798086; 840526</t>
+          <t>798098; 841871</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>610876; 632742</t>
+          <t>611730; 632430</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1419630; 1476661</t>
+          <t>1416810; 1477451</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2245967; 2556099</t>
+          <t>2244857; 2538854</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2109104; 2434830</t>
+          <t>2103489; 2435349</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4422301; 4867367</t>
+          <t>4404259; 4859959</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P39A2_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P39A2_2023-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>69,14%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65,13; 77,15</t>
+          <t>64,89; 75,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>64,44; 72,98</t>
+          <t>63,94; 72,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66,24; 73,64</t>
+          <t>65,66; 72,58</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,67%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>66,2; 76,85</t>
+          <t>65,6; 75,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,64; 69,46</t>
+          <t>62,21; 69,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65,52; 72,23</t>
+          <t>65,24; 71,56</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,33%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55,12; 66,43</t>
+          <t>55,36; 66,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45,18; 55,85</t>
+          <t>45,23; 54,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51,75; 59,27</t>
+          <t>51,59; 58,9</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>92,9%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>91,46; 96,94</t>
+          <t>88,14; 96,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,36; 93,38</t>
+          <t>88,76; 94,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56,58; 94,15</t>
+          <t>90,6; 94,99</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>26,3%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,01; 36,76</t>
+          <t>26,15; 38,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,8; 24,63</t>
+          <t>17,51; 25,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21,28; 28,24</t>
+          <t>22,97; 30,1</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,35%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>77,48; 87,07</t>
+          <t>78,02; 87,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>82,03; 89,63</t>
+          <t>81,96; 89,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81,16; 87,25</t>
+          <t>81,23; 86,96</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>45,33%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>43,58; 54,44</t>
+          <t>43,33; 52,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>42,14; 81,51</t>
+          <t>38,83; 46,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45,1; 71,89</t>
+          <t>42,45; 48,34</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>93,89%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>93,25; 98,36</t>
+          <t>91,92; 95,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>92,63; 95,77</t>
+          <t>91,79; 95,26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>93,44; 97,44</t>
+          <t>92,45; 95,14</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>69,06%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>70,48; 79,71</t>
+          <t>69,14; 72,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>63,93; 74,02</t>
+          <t>65,86; 68,54</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>68,02; 75,06</t>
+          <t>68,01; 70,25</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>221630</t>
+          <t>222888</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>195277</t>
+          <t>212500</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>416906</t>
+          <t>435388</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>202372; 239721</t>
+          <t>206383; 239837</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>182821; 207035</t>
+          <t>199266; 225082</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>393743; 437703</t>
+          <t>413474; 457048</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>364034</t>
+          <t>368155</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>316939</t>
+          <t>338923</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>680974</t>
+          <t>707078</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>335801; 389833</t>
+          <t>339901; 391535</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>296720; 334382</t>
+          <t>318248; 357889</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>647780; 714101</t>
+          <t>671748; 736819</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>146479</t>
+          <t>148123</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>316057</t>
+          <t>317701</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>153706; 185236</t>
+          <t>153978; 186226</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>130989; 161939</t>
+          <t>133895; 161983</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>294354; 337126</t>
+          <t>296185; 338182</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>230220</t>
+          <t>262471</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>272905</t>
+          <t>304656</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>503124</t>
+          <t>567127</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>222813; 236165</t>
+          <t>247395; 270239</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>150924; 340742</t>
+          <t>292739; 312714</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>344326; 572928</t>
+          <t>553111; 579885</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>52513</t>
+          <t>63936</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>42088</t>
+          <t>48039</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>94601</t>
+          <t>111975</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>41952; 64239</t>
+          <t>52638; 76902</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34684; 50856</t>
+          <t>39290; 58292</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>81119; 107670</t>
+          <t>97793; 128133</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>203071</t>
+          <t>200328</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>193647</t>
+          <t>197636</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>396718</t>
+          <t>397963</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>189489; 212954</t>
+          <t>188518; 210258</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>184077; 201124</t>
+          <t>188617; 204915</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>380607; 409148</t>
+          <t>383241; 410273</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>277231</t>
+          <t>315977</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>453623</t>
+          <t>291020</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>730853</t>
+          <t>606997</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>248116; 309978</t>
+          <t>283237; 344339</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>328228; 634870</t>
+          <t>266182; 316682</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>608132; 969253</t>
+          <t>568422; 647284</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>819518</t>
+          <t>665869</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>622992</t>
+          <t>712342</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1442509</t>
+          <t>1378211</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>798098; 841871</t>
+          <t>650528; 677913</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>611730; 632430</t>
+          <t>697828; 724172</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1416810; 1477451</t>
+          <t>1357090; 1396594</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2337794</t>
+          <t>2269200</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2243949</t>
+          <t>2253240</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4581743</t>
+          <t>4522440</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2244857; 2538854</t>
+          <t>2212180; 2321968</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2103489; 2435349</t>
+          <t>2205773; 2295612</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4404259; 4859959</t>
+          <t>4453543; 4600677</t>
         </is>
       </c>
     </row>
